--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 5.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 5.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4F194C-96B5-463B-9655-A8BA7F6E9360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -147,7 +146,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -321,7 +320,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,16 +355,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -377,35 +406,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -434,9 +436,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -474,9 +476,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -511,7 +513,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -546,7 +548,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,7 +721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -744,33 +746,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -807,10 +809,10 @@
       <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="21"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -822,18 +824,36 @@
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="11" t="str">
+        <f>VLOOKUP(C4,$M$4:$N$7,2,FALSE)</f>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="11"/>
+      <c r="F4" s="11" t="str">
+        <f>VLOOKUP(E4,$M$10:$O$14,2,FALSE)</f>
+        <v>Buku Tulis isi 50</v>
+      </c>
       <c r="G4" s="6">
         <v>332</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
+      <c r="H4" s="13">
+        <f>VLOOKUP(E4,$M$10:$O$14,3,FALSE)</f>
+        <v>200000</v>
+      </c>
+      <c r="I4" s="13">
+        <f>G4*H4</f>
+        <v>66400000</v>
+      </c>
+      <c r="J4" s="31">
+        <f>IF(G4&lt;200,0%,IF(G4&gt;500,20%,10%))</f>
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="13">
+        <f>I4-(I4*J4)</f>
+        <v>59760000</v>
+      </c>
       <c r="M4" s="9" t="s">
         <v>14</v>
       </c>
@@ -851,18 +871,36 @@
       <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="16" t="str">
+        <f t="shared" ref="D5:D18" si="0">VLOOKUP(C5,$M$4:$N$7,2,FALSE)</f>
+        <v>Toko Andi</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="16" t="str">
+        <f t="shared" ref="F5:F18" si="1">VLOOKUP(E5,$M$10:$O$14,2,FALSE)</f>
+        <v>Bulu Tulis Isi 100</v>
+      </c>
       <c r="G5" s="6">
         <v>203</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="13"/>
+      <c r="H5" s="13">
+        <f t="shared" ref="H5:H18" si="2">VLOOKUP(E5,$M$10:$O$14,3,FALSE)</f>
+        <v>375000</v>
+      </c>
+      <c r="I5" s="13">
+        <f t="shared" ref="I5:I18" si="3">G5*H5</f>
+        <v>76125000</v>
+      </c>
+      <c r="J5" s="31">
+        <f t="shared" ref="J5:J18" si="4">IF(G5&lt;200,0%,IF(G5&gt;500,20%,10%))</f>
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" ref="K5:K18" si="5">I5-(I5*J5)</f>
+        <v>68512500</v>
+      </c>
       <c r="M5" s="6" t="s">
         <v>12</v>
       </c>
@@ -880,18 +918,36 @@
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 5</v>
+      </c>
       <c r="G6" s="6">
         <v>176</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="13"/>
+      <c r="H6" s="13">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="I6" s="13">
+        <f t="shared" si="3"/>
+        <v>17600000</v>
+      </c>
+      <c r="J6" s="31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="5"/>
+        <v>17600000</v>
+      </c>
       <c r="M6" s="6" t="s">
         <v>16</v>
       </c>
@@ -909,18 +965,36 @@
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="E7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 10</v>
+      </c>
       <c r="G7" s="6">
         <v>248</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="13"/>
+      <c r="H7" s="13">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="I7" s="13">
+        <f t="shared" si="3"/>
+        <v>45880000</v>
+      </c>
+      <c r="J7" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="13">
+        <f t="shared" si="5"/>
+        <v>41292000</v>
+      </c>
       <c r="M7" s="6" t="s">
         <v>13</v>
       </c>
@@ -938,18 +1012,36 @@
       <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Andi</v>
+      </c>
       <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Buku Tulis isi 50</v>
+      </c>
       <c r="G8" s="6">
         <v>362</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="13"/>
+      <c r="H8" s="13">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="I8" s="13">
+        <f t="shared" si="3"/>
+        <v>72400000</v>
+      </c>
+      <c r="J8" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="13">
+        <f t="shared" si="5"/>
+        <v>65160000</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -961,23 +1053,41 @@
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Bulu Tulis Isi 100</v>
+      </c>
       <c r="G9" s="6">
         <v>354</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="13"/>
-      <c r="M9" s="21" t="s">
+      <c r="H9" s="13">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="I9" s="13">
+        <f t="shared" si="3"/>
+        <v>132750000</v>
+      </c>
+      <c r="J9" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="13">
+        <f t="shared" si="5"/>
+        <v>119475000</v>
+      </c>
+      <c r="M9" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
@@ -989,18 +1099,36 @@
       <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Andi</v>
+      </c>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 5</v>
+      </c>
       <c r="G10" s="6">
         <v>50</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="13"/>
+      <c r="H10" s="13">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="I10" s="13">
+        <f t="shared" si="3"/>
+        <v>5000000</v>
+      </c>
+      <c r="J10" s="31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="13">
+        <f t="shared" si="5"/>
+        <v>5000000</v>
+      </c>
       <c r="M10" s="9" t="s">
         <v>14</v>
       </c>
@@ -1021,18 +1149,36 @@
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 10</v>
+      </c>
       <c r="G11" s="6">
         <v>406</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="13"/>
+      <c r="H11" s="13">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="I11" s="13">
+        <f t="shared" si="3"/>
+        <v>75110000</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K11" s="13">
+        <f t="shared" si="5"/>
+        <v>67599000</v>
+      </c>
       <c r="M11" s="6" t="s">
         <v>32</v>
       </c>
@@ -1053,18 +1199,36 @@
       <c r="C12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Buku Tulis isi 50</v>
+      </c>
       <c r="G12" s="6">
         <v>202</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="13"/>
+      <c r="H12" s="13">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="I12" s="13">
+        <f t="shared" si="3"/>
+        <v>40400000</v>
+      </c>
+      <c r="J12" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="13">
+        <f t="shared" si="5"/>
+        <v>36360000</v>
+      </c>
       <c r="M12" s="6" t="s">
         <v>33</v>
       </c>
@@ -1085,18 +1249,36 @@
       <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Andi</v>
+      </c>
       <c r="E13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Bulu Tulis Isi 100</v>
+      </c>
       <c r="G13" s="6">
         <v>423</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="13"/>
+      <c r="H13" s="13">
+        <f t="shared" si="2"/>
+        <v>375000</v>
+      </c>
+      <c r="I13" s="13">
+        <f t="shared" si="3"/>
+        <v>158625000</v>
+      </c>
+      <c r="J13" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="13">
+        <f t="shared" si="5"/>
+        <v>142762500</v>
+      </c>
       <c r="M13" s="6" t="s">
         <v>18</v>
       </c>
@@ -1117,18 +1299,36 @@
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 5</v>
+      </c>
       <c r="G14" s="6">
         <v>156</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="13"/>
+      <c r="H14" s="13">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="I14" s="13">
+        <f t="shared" si="3"/>
+        <v>15600000</v>
+      </c>
+      <c r="J14" s="31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="13">
+        <f t="shared" si="5"/>
+        <v>15600000</v>
+      </c>
       <c r="M14" s="6" t="s">
         <v>19</v>
       </c>
@@ -1149,18 +1349,36 @@
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 10</v>
+      </c>
       <c r="G15" s="6">
         <v>600</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="13"/>
+      <c r="H15" s="13">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>111000000</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="13">
+        <f t="shared" si="5"/>
+        <v>88800000</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
@@ -1172,18 +1390,36 @@
       <c r="C16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Andi</v>
+      </c>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 5</v>
+      </c>
       <c r="G16" s="6">
         <v>454</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="13"/>
+      <c r="H16" s="13">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="I16" s="13">
+        <f t="shared" si="3"/>
+        <v>45400000</v>
+      </c>
+      <c r="J16" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="13">
+        <f t="shared" si="5"/>
+        <v>40860000</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -1195,18 +1431,36 @@
       <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Nafa</v>
+      </c>
       <c r="E17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 10</v>
+      </c>
       <c r="G17" s="6">
         <v>361</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="13"/>
+      <c r="H17" s="13">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="I17" s="13">
+        <f t="shared" si="3"/>
+        <v>66785000</v>
+      </c>
+      <c r="J17" s="31">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="13">
+        <f t="shared" si="5"/>
+        <v>60106500</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
@@ -1218,62 +1472,92 @@
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Toko Central</v>
+      </c>
       <c r="E18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pensil Box Isi 10</v>
+      </c>
       <c r="G18" s="6">
         <v>555</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="13"/>
+      <c r="H18" s="13">
+        <f t="shared" si="2"/>
+        <v>185000</v>
+      </c>
+      <c r="I18" s="13">
+        <f t="shared" si="3"/>
+        <v>102675000</v>
+      </c>
+      <c r="J18" s="31">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="13">
+        <f t="shared" si="5"/>
+        <v>82140000</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="12"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="12">
+        <f>SUM(G4:G18)</f>
+        <v>4882</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="12">
+        <f>SUM(K4:K18)</f>
+        <v>911027500</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="15"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="12">
+        <f>AVERAGE(G4:G18)</f>
+        <v>325.46666666666664</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="14">
+        <f>AVERAGE(K4:K18)</f>
+        <v>60735166.666666664</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="30" t="s">
+      <c r="C21" s="26"/>
+      <c r="D21" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1291,10 +1575,10 @@
       <c r="K22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="28"/>
+      <c r="M22" s="25"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1306,12 +1590,18 @@
       <c r="H23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="16"/>
+      <c r="I23" s="15">
+        <f>SUMIF($D$4:$D$18,H23,$K$4:$K$18)</f>
+        <v>411340500</v>
+      </c>
       <c r="K23" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
+      <c r="L23" s="17">
+        <f>SUMIF($F$4:$F$18,K23,$G$4:$G$18)</f>
+        <v>896</v>
+      </c>
+      <c r="M23" s="17"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1323,12 +1613,18 @@
       <c r="H24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="16"/>
+      <c r="I24" s="15">
+        <f t="shared" ref="I24:I25" si="6">SUMIF($D$4:$D$18,H24,$K$4:$K$18)</f>
+        <v>322295000</v>
+      </c>
       <c r="K24" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
+      <c r="L24" s="17">
+        <f t="shared" ref="L24:L26" si="7">SUMIF($F$4:$F$18,K24,$G$4:$G$18)</f>
+        <v>980</v>
+      </c>
+      <c r="M24" s="17"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -1340,12 +1636,18 @@
       <c r="H25" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="16"/>
+      <c r="I25" s="15">
+        <f t="shared" si="6"/>
+        <v>177392000</v>
+      </c>
       <c r="K25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
+      <c r="L25" s="17">
+        <f t="shared" si="7"/>
+        <v>836</v>
+      </c>
+      <c r="M25" s="17"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -1357,8 +1659,11 @@
       <c r="K26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
+      <c r="L26" s="17">
+        <f t="shared" si="7"/>
+        <v>2170</v>
+      </c>
+      <c r="M26" s="17"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1370,11 +1675,7 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A1:K2"/>
     <mergeCell ref="H19:J20"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="L23:M23"/>
@@ -1382,10 +1683,14 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M9:O9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D21" r:id="rId1" xr:uid="{EFE1958D-EB2F-4E58-AFCD-DD22B8E85F1E}"/>
+    <hyperlink ref="D21" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 5.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 5.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4F194C-96B5-463B-9655-A8BA7F6E9360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -146,7 +147,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -320,7 +321,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -355,59 +356,56 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -436,9 +434,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -476,9 +474,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -513,7 +511,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -548,7 +546,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -721,7 +719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -746,33 +744,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -809,10 +807,10 @@
       <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="18"/>
+      <c r="N3" s="21"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -824,36 +822,18 @@
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="11" t="str">
-        <f>VLOOKUP(C4,$M$4:$N$7,2,FALSE)</f>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D4" s="11"/>
       <c r="E4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="11" t="str">
-        <f>VLOOKUP(E4,$M$10:$O$14,2,FALSE)</f>
-        <v>Buku Tulis isi 50</v>
-      </c>
+      <c r="F4" s="11"/>
       <c r="G4" s="6">
         <v>332</v>
       </c>
-      <c r="H4" s="13">
-        <f>VLOOKUP(E4,$M$10:$O$14,3,FALSE)</f>
-        <v>200000</v>
-      </c>
-      <c r="I4" s="13">
-        <f>G4*H4</f>
-        <v>66400000</v>
-      </c>
-      <c r="J4" s="31">
-        <f>IF(G4&lt;200,0%,IF(G4&gt;500,20%,10%))</f>
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="13">
-        <f>I4-(I4*J4)</f>
-        <v>59760000</v>
-      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="13"/>
       <c r="M4" s="9" t="s">
         <v>14</v>
       </c>
@@ -871,36 +851,18 @@
       <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="16" t="str">
-        <f t="shared" ref="D5:D18" si="0">VLOOKUP(C5,$M$4:$N$7,2,FALSE)</f>
-        <v>Toko Andi</v>
-      </c>
+      <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="16" t="str">
-        <f t="shared" ref="F5:F18" si="1">VLOOKUP(E5,$M$10:$O$14,2,FALSE)</f>
-        <v>Bulu Tulis Isi 100</v>
-      </c>
+      <c r="F5" s="11"/>
       <c r="G5" s="6">
         <v>203</v>
       </c>
-      <c r="H5" s="13">
-        <f t="shared" ref="H5:H18" si="2">VLOOKUP(E5,$M$10:$O$14,3,FALSE)</f>
-        <v>375000</v>
-      </c>
-      <c r="I5" s="13">
-        <f t="shared" ref="I5:I18" si="3">G5*H5</f>
-        <v>76125000</v>
-      </c>
-      <c r="J5" s="31">
-        <f t="shared" ref="J5:J18" si="4">IF(G5&lt;200,0%,IF(G5&gt;500,20%,10%))</f>
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" ref="K5:K18" si="5">I5-(I5*J5)</f>
-        <v>68512500</v>
-      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="13"/>
       <c r="M5" s="6" t="s">
         <v>12</v>
       </c>
@@ -918,36 +880,18 @@
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="D6" s="11"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 5</v>
-      </c>
+      <c r="F6" s="11"/>
       <c r="G6" s="6">
         <v>176</v>
       </c>
-      <c r="H6" s="13">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="3"/>
-        <v>17600000</v>
-      </c>
-      <c r="J6" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="5"/>
-        <v>17600000</v>
-      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="13"/>
       <c r="M6" s="6" t="s">
         <v>16</v>
       </c>
@@ -965,36 +909,18 @@
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="D7" s="11"/>
       <c r="E7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 10</v>
-      </c>
+      <c r="F7" s="11"/>
       <c r="G7" s="6">
         <v>248</v>
       </c>
-      <c r="H7" s="13">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="I7" s="13">
-        <f t="shared" si="3"/>
-        <v>45880000</v>
-      </c>
-      <c r="J7" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="13">
-        <f t="shared" si="5"/>
-        <v>41292000</v>
-      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="13"/>
       <c r="M7" s="6" t="s">
         <v>13</v>
       </c>
@@ -1012,36 +938,18 @@
       <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Andi</v>
-      </c>
+      <c r="D8" s="11"/>
       <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Buku Tulis isi 50</v>
-      </c>
+      <c r="F8" s="11"/>
       <c r="G8" s="6">
         <v>362</v>
       </c>
-      <c r="H8" s="13">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="I8" s="13">
-        <f t="shared" si="3"/>
-        <v>72400000</v>
-      </c>
-      <c r="J8" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="13">
-        <f t="shared" si="5"/>
-        <v>65160000</v>
-      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1053,41 +961,23 @@
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D9" s="11"/>
       <c r="E9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Bulu Tulis Isi 100</v>
-      </c>
+      <c r="F9" s="11"/>
       <c r="G9" s="6">
         <v>354</v>
       </c>
-      <c r="H9" s="13">
-        <f t="shared" si="2"/>
-        <v>375000</v>
-      </c>
-      <c r="I9" s="13">
-        <f t="shared" si="3"/>
-        <v>132750000</v>
-      </c>
-      <c r="J9" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="13">
-        <f t="shared" si="5"/>
-        <v>119475000</v>
-      </c>
-      <c r="M9" s="18" t="s">
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="13"/>
+      <c r="M9" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
@@ -1099,36 +989,18 @@
       <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Andi</v>
-      </c>
+      <c r="D10" s="11"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 5</v>
-      </c>
+      <c r="F10" s="11"/>
       <c r="G10" s="6">
         <v>50</v>
       </c>
-      <c r="H10" s="13">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="I10" s="13">
-        <f t="shared" si="3"/>
-        <v>5000000</v>
-      </c>
-      <c r="J10" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <f t="shared" si="5"/>
-        <v>5000000</v>
-      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="13"/>
       <c r="M10" s="9" t="s">
         <v>14</v>
       </c>
@@ -1149,36 +1021,18 @@
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D11" s="11"/>
       <c r="E11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 10</v>
-      </c>
+      <c r="F11" s="11"/>
       <c r="G11" s="6">
         <v>406</v>
       </c>
-      <c r="H11" s="13">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="I11" s="13">
-        <f t="shared" si="3"/>
-        <v>75110000</v>
-      </c>
-      <c r="J11" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K11" s="13">
-        <f t="shared" si="5"/>
-        <v>67599000</v>
-      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="13"/>
       <c r="M11" s="6" t="s">
         <v>32</v>
       </c>
@@ -1199,36 +1053,18 @@
       <c r="C12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="D12" s="11"/>
       <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Buku Tulis isi 50</v>
-      </c>
+      <c r="F12" s="11"/>
       <c r="G12" s="6">
         <v>202</v>
       </c>
-      <c r="H12" s="13">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="I12" s="13">
-        <f t="shared" si="3"/>
-        <v>40400000</v>
-      </c>
-      <c r="J12" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="13">
-        <f t="shared" si="5"/>
-        <v>36360000</v>
-      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="13"/>
       <c r="M12" s="6" t="s">
         <v>33</v>
       </c>
@@ -1249,36 +1085,18 @@
       <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Andi</v>
-      </c>
+      <c r="D13" s="11"/>
       <c r="E13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Bulu Tulis Isi 100</v>
-      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="6">
         <v>423</v>
       </c>
-      <c r="H13" s="13">
-        <f t="shared" si="2"/>
-        <v>375000</v>
-      </c>
-      <c r="I13" s="13">
-        <f t="shared" si="3"/>
-        <v>158625000</v>
-      </c>
-      <c r="J13" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="13">
-        <f t="shared" si="5"/>
-        <v>142762500</v>
-      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="13"/>
       <c r="M13" s="6" t="s">
         <v>18</v>
       </c>
@@ -1299,36 +1117,18 @@
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D14" s="11"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 5</v>
-      </c>
+      <c r="F14" s="11"/>
       <c r="G14" s="6">
         <v>156</v>
       </c>
-      <c r="H14" s="13">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="I14" s="13">
-        <f t="shared" si="3"/>
-        <v>15600000</v>
-      </c>
-      <c r="J14" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="13">
-        <f t="shared" si="5"/>
-        <v>15600000</v>
-      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="13"/>
       <c r="M14" s="6" t="s">
         <v>19</v>
       </c>
@@ -1349,36 +1149,18 @@
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D15" s="11"/>
       <c r="E15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 10</v>
-      </c>
+      <c r="F15" s="11"/>
       <c r="G15" s="6">
         <v>600</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="3"/>
-        <v>111000000</v>
-      </c>
-      <c r="J15" s="31">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="K15" s="13">
-        <f t="shared" si="5"/>
-        <v>88800000</v>
-      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
@@ -1390,36 +1172,18 @@
       <c r="C16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Andi</v>
-      </c>
+      <c r="D16" s="11"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 5</v>
-      </c>
+      <c r="F16" s="11"/>
       <c r="G16" s="6">
         <v>454</v>
       </c>
-      <c r="H16" s="13">
-        <f t="shared" si="2"/>
-        <v>100000</v>
-      </c>
-      <c r="I16" s="13">
-        <f t="shared" si="3"/>
-        <v>45400000</v>
-      </c>
-      <c r="J16" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K16" s="13">
-        <f t="shared" si="5"/>
-        <v>40860000</v>
-      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -1431,36 +1195,18 @@
       <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Nafa</v>
-      </c>
+      <c r="D17" s="11"/>
       <c r="E17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 10</v>
-      </c>
+      <c r="F17" s="11"/>
       <c r="G17" s="6">
         <v>361</v>
       </c>
-      <c r="H17" s="13">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="I17" s="13">
-        <f t="shared" si="3"/>
-        <v>66785000</v>
-      </c>
-      <c r="J17" s="31">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="K17" s="13">
-        <f t="shared" si="5"/>
-        <v>60106500</v>
-      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="13"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
@@ -1472,92 +1218,62 @@
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>Toko Central</v>
-      </c>
+      <c r="D18" s="11"/>
       <c r="E18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>Pensil Box Isi 10</v>
-      </c>
+      <c r="F18" s="11"/>
       <c r="G18" s="6">
         <v>555</v>
       </c>
-      <c r="H18" s="13">
-        <f t="shared" si="2"/>
-        <v>185000</v>
-      </c>
-      <c r="I18" s="13">
-        <f t="shared" si="3"/>
-        <v>102675000</v>
-      </c>
-      <c r="J18" s="31">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-      <c r="K18" s="13">
-        <f t="shared" si="5"/>
-        <v>82140000</v>
-      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="12">
-        <f>SUM(G4:G18)</f>
-        <v>4882</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="12">
-        <f>SUM(K4:K18)</f>
-        <v>911027500</v>
-      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="12">
-        <f>AVERAGE(G4:G18)</f>
-        <v>325.46666666666664</v>
-      </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="14">
-        <f>AVERAGE(K4:K18)</f>
-        <v>60735166.666666664</v>
-      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1575,10 +1291,10 @@
       <c r="K22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="25" t="s">
+      <c r="L22" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="25"/>
+      <c r="M22" s="28"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1590,18 +1306,12 @@
       <c r="H23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="15">
-        <f>SUMIF($D$4:$D$18,H23,$K$4:$K$18)</f>
-        <v>411340500</v>
-      </c>
+      <c r="I23" s="16"/>
       <c r="K23" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="17">
-        <f>SUMIF($F$4:$F$18,K23,$G$4:$G$18)</f>
-        <v>896</v>
-      </c>
-      <c r="M23" s="17"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1613,18 +1323,12 @@
       <c r="H24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="15">
-        <f t="shared" ref="I24:I25" si="6">SUMIF($D$4:$D$18,H24,$K$4:$K$18)</f>
-        <v>322295000</v>
-      </c>
+      <c r="I24" s="16"/>
       <c r="K24" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L24" s="17">
-        <f t="shared" ref="L24:L26" si="7">SUMIF($F$4:$F$18,K24,$G$4:$G$18)</f>
-        <v>980</v>
-      </c>
-      <c r="M24" s="17"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -1636,18 +1340,12 @@
       <c r="H25" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="15">
-        <f t="shared" si="6"/>
-        <v>177392000</v>
-      </c>
+      <c r="I25" s="16"/>
       <c r="K25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="17">
-        <f t="shared" si="7"/>
-        <v>836</v>
-      </c>
-      <c r="M25" s="17"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -1659,11 +1357,8 @@
       <c r="K26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L26" s="17">
-        <f t="shared" si="7"/>
-        <v>2170</v>
-      </c>
-      <c r="M26" s="17"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1675,7 +1370,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M9:O9"/>
     <mergeCell ref="H19:J20"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="L23:M23"/>
@@ -1683,14 +1382,10 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A1:K2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D21" r:id="rId1"/>
+    <hyperlink ref="D21" r:id="rId1" xr:uid="{EFE1958D-EB2F-4E58-AFCD-DD22B8E85F1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
